--- a/data/trans_camb/P05A_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P05A_R-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-11,87</t>
+          <t>-12,29</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-16,61</t>
+          <t>-16,29</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-14,59</t>
+          <t>-14,56</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,54; 10,92</t>
+          <t>2,57; 11,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 9,25</t>
+          <t>0,37; 9,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,9; -7,28</t>
+          <t>-16,51; -8,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 8,9</t>
+          <t>1,48; 8,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 3,86</t>
+          <t>-4,31; 3,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,98; -13,32</t>
+          <t>-19,67; -12,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,4; 9,03</t>
+          <t>2,88; 8,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 5,02</t>
+          <t>-1,11; 4,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-17,27; -11,95</t>
+          <t>-17,09; -11,81</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-37,58%</t>
+          <t>-38,9%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-48,24%</t>
+          <t>-47,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-43,98%</t>
+          <t>-43,89%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,56; 36,6</t>
+          <t>7,56; 39,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 30,81</t>
+          <t>1,31; 30,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-48,11; -24,96</t>
+          <t>-49,99; -27,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,61; 27,17</t>
+          <t>4,09; 27,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 11,94</t>
+          <t>-12,0; 10,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-55,03; -40,47</t>
+          <t>-54,57; -39,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,92; 28,45</t>
+          <t>8,92; 28,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 15,83</t>
+          <t>-3,21; 14,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-50,09; -37,47</t>
+          <t>-49,81; -36,73</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-12,36</t>
+          <t>-10,15</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-8,74</t>
+          <t>-14,74</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-10,49</t>
+          <t>-12,35</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,75; 15,43</t>
+          <t>9,02; 15,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,27; 10,35</t>
+          <t>4,34; 10,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,31; -8,94</t>
+          <t>-12,86; -7,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 7,92</t>
+          <t>1,26; 7,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 5,2</t>
+          <t>-1,42; 5,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-17,06; 9,28</t>
+          <t>-17,69; -11,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,14; 10,7</t>
+          <t>5,73; 10,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,49; 6,98</t>
+          <t>2,46; 6,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-15,27; 2,15</t>
+          <t>-14,4; -10,35</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-45,28%</t>
+          <t>-37,18%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-25,16%</t>
+          <t>-42,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-33,97%</t>
+          <t>-39,96%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30,34; 60,14</t>
+          <t>31,16; 59,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,63; 40,76</t>
+          <t>14,96; 39,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-61,87; -34,58</t>
+          <t>-45,33; -28,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,0; 24,42</t>
+          <t>3,29; 23,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 15,96</t>
+          <t>-3,95; 16,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-48,59; 27,04</t>
+          <t>-48,39; -36,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,28; 36,13</t>
+          <t>18,02; 35,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,97; 23,7</t>
+          <t>7,67; 23,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-49,02; 6,93</t>
+          <t>-44,52; -34,58</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-9,42</t>
+          <t>-10,18</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-9,6</t>
+          <t>-9,44</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-9,48</t>
+          <t>-9,77</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,54; 17,99</t>
+          <t>4,77; 17,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 13,65</t>
+          <t>2,05; 14,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,65; -2,88</t>
+          <t>-15,76; -4,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,98; 17,08</t>
+          <t>4,24; 16,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,77; 13,6</t>
+          <t>1,28; 14,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,1; -4,18</t>
+          <t>-15,1; -4,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,55; 15,59</t>
+          <t>6,26; 15,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,73; 12,37</t>
+          <t>3,33; 11,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-13,49; -5,41</t>
+          <t>-13,22; -5,77</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-28,99%</t>
+          <t>-31,32%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-28,85%</t>
+          <t>-28,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-28,85%</t>
+          <t>-29,73%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,52; 61,0</t>
+          <t>13,4; 59,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,76; 45,76</t>
+          <t>5,42; 46,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-41,81; -9,77</t>
+          <t>-44,03; -14,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10,71; 56,19</t>
+          <t>11,65; 56,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,82; 45,09</t>
+          <t>3,41; 46,35</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-41,15; -14,63</t>
+          <t>-40,59; -14,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,7; 50,67</t>
+          <t>17,74; 49,72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,67; 40,36</t>
+          <t>9,83; 38,94</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-38,6; -17,65</t>
+          <t>-37,96; -19,21</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-12,35</t>
+          <t>-10,98</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-10,52</t>
+          <t>-14,07</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-11,38</t>
+          <t>-12,53</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,86; 12,52</t>
+          <t>7,89; 12,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,37; 8,92</t>
+          <t>4,07; 8,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,16; -9,81</t>
+          <t>-13,08; -8,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,92; 7,59</t>
+          <t>2,86; 7,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 4,46</t>
+          <t>0,11; 4,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,94; 3,87</t>
+          <t>-16,0; -11,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,17; 9,56</t>
+          <t>5,91; 9,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,79; 5,99</t>
+          <t>2,69; 5,95</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-14,34; -1,67</t>
+          <t>-14,01; -11,18</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-41,82%</t>
+          <t>-37,18%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-30,58%</t>
+          <t>-40,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-35,55%</t>
+          <t>-39,16%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>25,61; 44,28</t>
+          <t>25,9; 43,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14,28; 31,33</t>
+          <t>13,11; 30,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-54,4; -34,36</t>
+          <t>-42,82; -31,03</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,31; 22,79</t>
+          <t>8,03; 23,16</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 13,29</t>
+          <t>0,25; 13,91</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-45,76; 11,66</t>
+          <t>-45,25; -36,01</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,86; 30,46</t>
+          <t>18,0; 29,81</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,51; 19,13</t>
+          <t>8,07; 18,86</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-44,48; -5,06</t>
+          <t>-42,73; -35,52</t>
         </is>
       </c>
     </row>
